--- a/paper/source_data/fig5_source_data.xlsx
+++ b/paper/source_data/fig5_source_data.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>One sheet per panel with exactly the plotted values, intervals, floored counts and labels. Each row names the aggregate file it was read from and that file's SHA-256.</t>
+          <t>One sheet per panel with exactly the plotted values, intervals, floored counts and labels. Each row names the aggregate file it was read from and that file's SHA-256, with one further column pair for each further file a row was read from.</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>**Fig. 5 | BRAN under missing inputs and in external cohorts without retinal images.** **a**, Inputs and history. People, development adults, eICU training exposure, INSPIRE test survivors and KNHANES adults fitting or testing **e** (≥, released lower bound). HiRID admissions, PLACEHOLDER. **b**,**c**, 26-condition macro AUROC in held-out AI-READI folds, clinical fields (**b**) or input blocks (**c**) withheld. Dashed line, all inputs. †, descriptive. Late fusion led without blood count or retina by 0.013 [0.007, 0.018]. **d**, Five-pattern means and paired differences, primary versus gradient boosting. Open marker, late fusion ahead. **b** to **d**, 1,928 adults, fewer than 20 abstentions per pattern (exact shares PLACEHOLDER). **e**, KNHANES 2024 locked test (5,600 adults, haemoglobin 5,360, 7 diagnoses). Key secondaries not met, one-sided Holm-adjusted P = 0.400 (label efficiency) and 0.084 (haemoglobin). In men the primary interval included zero, BRAN trailed at 500 labels and native haemoglobin bias differed by sex. **f**, INSPIRE surgical mortality (≥17,660 survivors, ≥80 deaths). Primary contrast versus blood tests plus context crossed zero (two-comparison adjusted). **g**, HiRID haemoglobin error, direct and local blocks on different admission sets. Direct-use nominal 90% intervals covered 0.41. Local BRAN tied raw inputs. Not drawn, earlier-checkpoint BRAN trailed raw readouts in 5 of 7 KNHANES 2022 to 2023 comparisons (support PLACEHOLDER), three KNHANES 2010 to 2012 studies tied and label budget was adverse (Extended Data Fig. 3e). Points, estimates. Bars, 95% bootstrap intervals (1,000 draws, linearized for haemoglobin in **e**), unadjusted unless stated, baseline bars in Source Data. Label-efficiency intervals omit subsample spread.</t>
+          <t>**Fig. 5 | BRAN under missing inputs and in external cohorts without retinal images.** **a**, Inputs and history. People, development adults, eICU training exposure, INSPIRE test survivors and KNHANES adults fitting or testing **e** (≥, released lower bound). HiRID admissions, PLACEHOLDER. **b**,**c**, 26-condition macro AUROC in held-out AI-READI folds, clinical fields (**b**) or input blocks (**c**) withheld. Dashed line, all inputs. †, descriptive. Late fusion led without blood count or retina by 0.013 [0.007, 0.018]. **d**, Five-pattern means and paired differences, primary versus gradient boosting. Open marker, late fusion ahead. **b** to **d**, 1,928 adults, fewer than 20 abstentions per pattern (exact shares PLACEHOLDER). **e**, KNHANES 2024 locked test (5,600 adults, haemoglobin 5,360, 7 diagnoses). Key secondaries not met, one-sided Holm-adjusted *P* = 0.400 (label efficiency) and 0.084 (haemoglobin). In men the primary interval included zero, BRAN trailed at 500 labels and native haemoglobin bias differed by sex. **f**, INSPIRE surgical mortality (≥17,660 survivors, ≥80 deaths). Primary contrast versus blood tests plus context crossed zero (two-comparison adjusted). **g**, HiRID haemoglobin error, direct and local blocks on different admission sets. Direct-use nominal 90% intervals covered 0.41. Local BRAN tied raw inputs. Not drawn, earlier-checkpoint BRAN trailed raw readouts in 5 of 7 KNHANES 2022 to 2023 comparisons (support PLACEHOLDER), three KNHANES 2010 to 2012 studies tied and label budget was adverse (Extended Data Fig. 3e). Points, estimates. Bars, 95% bootstrap intervals (1,000 draws, linearized for haemoglobin in **e**), unadjusted unless stated, baseline bars in Source Data. Label-efficiency intervals omit subsample spread.</t>
         </is>
       </c>
     </row>
@@ -8226,13 +8226,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3.327063977702394</v>
+        <v>3.327</v>
       </c>
       <c r="E6" t="n">
-        <v>3.290957270343875</v>
+        <v>3.291</v>
       </c>
       <c r="F6" t="n">
-        <v>3.367457707330242</v>
+        <v>3.367</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -8267,16 +8267,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2.618946332215809</v>
+        <v>2.619</v>
       </c>
       <c r="E7" t="n">
-        <v>2.587975803931247</v>
+        <v>2.588</v>
       </c>
       <c r="F7" t="n">
-        <v>2.654122430728853</v>
+        <v>2.654</v>
       </c>
       <c r="G7" t="n">
-        <v>2.310354307262404</v>
+        <v>2.31</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -8311,13 +8311,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.639505462909719</v>
+        <v>1.64</v>
       </c>
       <c r="E8" t="n">
-        <v>1.58179455585844</v>
+        <v>1.582</v>
       </c>
       <c r="F8" t="n">
-        <v>1.694362868190134</v>
+        <v>1.694</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -8352,13 +8352,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.634111383562014</v>
+        <v>1.634</v>
       </c>
       <c r="E9" t="n">
-        <v>1.57828908907277</v>
+        <v>1.578</v>
       </c>
       <c r="F9" t="n">
-        <v>1.690717715309127</v>
+        <v>1.691</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -8393,13 +8393,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.65419911840016</v>
+        <v>1.654</v>
       </c>
       <c r="E10" t="n">
-        <v>1.596004262003296</v>
+        <v>1.596</v>
       </c>
       <c r="F10" t="n">
-        <v>1.709205678940831</v>
+        <v>1.709</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -8434,13 +8434,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.632618905954741</v>
+        <v>1.633</v>
       </c>
       <c r="E11" t="n">
-        <v>1.576248425900128</v>
+        <v>1.576</v>
       </c>
       <c r="F11" t="n">
-        <v>1.688661107085806</v>
+        <v>1.689</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
